--- a/downloads/blackcat-airbnb-profit-tracker.xlsx
+++ b/downloads/blackcat-airbnb-profit-tracker.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="176">
   <si>
-    <t>🐈‍⬛ Black Cat Analytics — Airbnb Profit Tracker</t>
+    <t>Black Cat Analytics — Airbnb Profit Tracker</t>
   </si>
   <si>
     <t/>
@@ -114,7 +114,7 @@
     <t>Questions? support@tryblackcat.com</t>
   </si>
   <si>
-    <t>🐈‍⬛ Black Cat Analytics — Revenue &amp; Expense Log</t>
+    <t>Black Cat Analytics — Revenue &amp; Expense Log</t>
   </si>
   <si>
     <t>Log every Airbnb payout and expense here. The other sheets pull from this data.</t>
@@ -273,7 +273,7 @@
     <t>3% of gross</t>
   </si>
   <si>
-    <t>🐈‍⬛ Black Cat Analytics — Monthly Dashboard</t>
+    <t>Black Cat Analytics — Monthly Dashboard</t>
   </si>
   <si>
     <t>Auto-calculated from your Revenue &amp; Expenses log. Do not edit the formula cells.</t>
@@ -339,7 +339,7 @@
     <t>Avg Revenue/Transaction</t>
   </si>
   <si>
-    <t>🐈‍⬛ Black Cat Analytics — Per-Property Summary</t>
+    <t>Black Cat Analytics — Per-Property Summary</t>
   </si>
   <si>
     <t>Performance breakdown by listing. Add your property names in column A.</t>
@@ -360,7 +360,7 @@
     <t>TOTAL</t>
   </si>
   <si>
-    <t>🐈‍⬛ Black Cat Analytics — Schedule E Tax Report</t>
+    <t>Black Cat Analytics — Schedule E Tax Report</t>
   </si>
   <si>
     <t>Auto-calculated deductions mapped to IRS Schedule E line items. Adjust "Fair Rental Days" and "Personal Use Days" below.</t>
@@ -474,7 +474,7 @@
     <t>NET RENTAL INCOME (Line 21)</t>
   </si>
   <si>
-    <t>🐈‍⬛ Black Cat Analytics — Cleaning Cost Tracker</t>
+    <t>Black Cat Analytics — Cleaning Cost Tracker</t>
   </si>
   <si>
     <t>Track per-turnover cleaning costs by property. Spot overcharges and optimize your biggest variable expense.</t>
@@ -806,6 +806,226 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="304800" cy="304800"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="304800" cy="304800"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="304800" cy="304800"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="304800" cy="304800"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="304800" cy="304800"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1337,11 +1557,10 @@
     <col min="8" max="8" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+    <row r="1" ht="40" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="4"/>
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
       <c r="E1" s="4"/>
@@ -2411,7 +2630,7 @@
     <row r="500" spans="2:7" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="B1:H1"/>
     <mergeCell ref="A2:H2"/>
   </mergeCells>
   <dataValidations count="6">
@@ -2436,6 +2655,7 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2449,11 +2669,10 @@
     <col min="14" max="14" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+    <row r="1" ht="40" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B1" s="4"/>
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
       <c r="E1" s="4"/>
@@ -2784,11 +3003,12 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="B1:H1"/>
     <mergeCell ref="A2:H2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2805,11 +3025,10 @@
     <col min="8" max="8" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+    <row r="1" ht="40" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="B1" s="4"/>
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
       <c r="E1" s="4"/>
@@ -2952,11 +3171,12 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="B1:H1"/>
     <mergeCell ref="A2:H2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2971,11 +3191,10 @@
     <col min="4" max="5" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+    <row r="1" ht="40" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="B1" s="4"/>
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
       <c r="E1" s="4"/>
@@ -3264,11 +3483,12 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="B1:H1"/>
     <mergeCell ref="A2:H2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3287,11 +3507,10 @@
     <col min="9" max="9" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+    <row r="1" ht="40" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="B1" s="4"/>
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
       <c r="E1" s="4"/>
@@ -3818,7 +4037,7 @@
     <row r="300" spans="7:8" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="B1:H1"/>
     <mergeCell ref="A2:H2"/>
   </mergeCells>
   <dataValidations count="4">
@@ -3837,5 +4056,6 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/downloads/blackcat-airbnb-profit-tracker.xlsx
+++ b/downloads/blackcat-airbnb-profit-tracker.xlsx
@@ -817,7 +817,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="304800" cy="304800"/>
+    <xdr:ext cx="419100" cy="419100"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="1" name="Picture 1">
@@ -861,7 +861,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="304800" cy="304800"/>
+    <xdr:ext cx="419100" cy="419100"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="1" name="Picture 1">
@@ -905,7 +905,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="304800" cy="304800"/>
+    <xdr:ext cx="419100" cy="419100"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="1" name="Picture 1">
@@ -949,7 +949,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="304800" cy="304800"/>
+    <xdr:ext cx="419100" cy="419100"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="1" name="Picture 1">
@@ -993,7 +993,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="304800" cy="304800"/>
+    <xdr:ext cx="419100" cy="419100"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="1" name="Picture 1">
@@ -1557,7 +1557,7 @@
     <col min="8" max="8" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="1" ht="48" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B1" s="4" t="s">
         <v>32</v>
       </c>
@@ -2669,7 +2669,7 @@
     <col min="14" max="14" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="1" ht="48" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B1" s="4" t="s">
         <v>85</v>
       </c>
@@ -3025,7 +3025,7 @@
     <col min="8" max="8" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="1" ht="48" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B1" s="4" t="s">
         <v>107</v>
       </c>
@@ -3191,7 +3191,7 @@
     <col min="4" max="5" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="1" ht="48" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B1" s="4" t="s">
         <v>114</v>
       </c>
@@ -3507,7 +3507,7 @@
     <col min="9" max="9" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="1" ht="48" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B1" s="4" t="s">
         <v>152</v>
       </c>

--- a/downloads/blackcat-airbnb-profit-tracker.xlsx
+++ b/downloads/blackcat-airbnb-profit-tracker.xlsx
@@ -108,7 +108,7 @@
     <t>generates tax reports, and gives you AI-powered insights.</t>
   </si>
   <si>
-    <t>→ https://app.tryblackcat.com/signup (Free to start)</t>
+    <t>→ https://app.tryblackcat.com/signup?utm_source=tryblackcat&amp;utm_medium=spreadsheet&amp;utm_content=xlsx_instructions (Free to start)</t>
   </si>
   <si>
     <t>Questions? support@tryblackcat.com</t>
@@ -270,7 +270,7 @@
     <t>Airbnb host fee — January</t>
   </si>
   <si>
-    <t>3% of gross</t>
+    <t>3% of gross (15.5% from Sept 15, 2026)</t>
   </si>
   <si>
     <t>Black Cat Analytics — Monthly Dashboard</t>

--- a/downloads/blackcat-airbnb-profit-tracker.xlsx
+++ b/downloads/blackcat-airbnb-profit-tracker.xlsx
@@ -16,9 +16,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="176">
-  <si>
-    <t>Black Cat Analytics — Airbnb Profit Tracker</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="190">
+  <si>
+    <t>Black Cat Analytics — Airbnb Profit Tracker (updated Sept 2026 for the 15.5% host fee)</t>
   </si>
   <si>
     <t/>
@@ -60,6 +60,27 @@
     <t>• Back up this file regularly — save a copy each month.</t>
   </si>
   <si>
+    <t>SEPT 15, 2026 — AIRBNB'S NEW 15.5% HOST FEE</t>
+  </si>
+  <si>
+    <t>• From Sept 15, 2026 (Oct 13 in the EEA) Airbnb charges hosts one 15.5% fee and drops the guest service fee. Before that, hosts paid 3%.</t>
+  </si>
+  <si>
+    <t>• Log the GROSS booking amount (what the guest paid before Airbnb's cut) as revenue, then log the 15.5% as its own "Platform Fees" expense.</t>
+  </si>
+  <si>
+    <t>• Why it matters: the 1099-K Airbnb sends the IRS reports GROSS. Logging only your net payout under-reports revenue and hides a deduction.</t>
+  </si>
+  <si>
+    <t>• Break-even repricing: raise prices about 14.8% (price ÷ 0.845) to keep your payout unchanged. +18.3% nets your full old sticker price.</t>
+  </si>
+  <si>
+    <t>• Free side-by-side calculator: https://www.tryblackcat.com/tools/airbnb-fee-calculator.html</t>
+  </si>
+  <si>
+    <t>• See the September sample rows in the Revenue &amp; Expenses tab for the gross + fee pattern.</t>
+  </si>
+  <si>
     <t>EXPENSE CATEGORIES (mapped to IRS Schedule E)</t>
   </si>
   <si>
@@ -156,7 +177,7 @@
     <t>Downtown Loft</t>
   </si>
   <si>
-    <t>Payout — 4 night stay (Martinez)</t>
+    <t>Gross booking — 4 night stay (Martinez)</t>
   </si>
   <si>
     <t>No</t>
@@ -183,7 +204,7 @@
     <t>Lakeside Cabin</t>
   </si>
   <si>
-    <t>Payout — 3 night stay (Chen)</t>
+    <t>Gross booking — 3 night stay (Chen)</t>
   </si>
   <si>
     <t>Turnover clean after Chen</t>
@@ -204,7 +225,7 @@
     <t>Beach Bungalow</t>
   </si>
   <si>
-    <t>Payout — 5 night stay (Johnson)</t>
+    <t>Gross booking — 5 night stay (Johnson)</t>
   </si>
   <si>
     <t>Deep clean after Johnson</t>
@@ -234,7 +255,7 @@
     <t>2026-01-22</t>
   </si>
   <si>
-    <t>Payout — 3 night stay (Williams)</t>
+    <t>Gross booking — 3 night stay (Williams)</t>
   </si>
   <si>
     <t>Turnover clean after Williams</t>
@@ -255,7 +276,7 @@
     <t>2026-01-28</t>
   </si>
   <si>
-    <t>Payout — 7 night stay (Davis)</t>
+    <t>Gross booking — 7 night stay (Davis)</t>
   </si>
   <si>
     <t>Deep clean after Davis (7 night)</t>
@@ -270,7 +291,28 @@
     <t>Airbnb host fee — January</t>
   </si>
   <si>
-    <t>3% of gross (15.5% from Sept 15, 2026)</t>
+    <t>3% of gross — the old fee, before Sept 15, 2026</t>
+  </si>
+  <si>
+    <t>2026-09-18</t>
+  </si>
+  <si>
+    <t>Gross booking — 4 night stay (Nguyen)</t>
+  </si>
+  <si>
+    <t>Gross amount, before Airbnb's 15.5% fee — matches your 1099-K</t>
+  </si>
+  <si>
+    <t>Airbnb host fee — 15.5% (new fee from Sept 15, 2026)</t>
+  </si>
+  <si>
+    <t>15.5% of gross → Schedule E Line 8</t>
+  </si>
+  <si>
+    <t>2026-09-19</t>
+  </si>
+  <si>
+    <t>Turnover clean after Nguyen</t>
   </si>
   <si>
     <t>Black Cat Analytics — Monthly Dashboard</t>
@@ -1350,7 +1392,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A36"/>
+  <dimension ref="A1:A44"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="80" customWidth="1"/>
@@ -1473,41 +1515,41 @@
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
         <v>21</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="s">
+      <c r="A31" s="2" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1528,12 +1570,52 @@
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>1</v>
+        <v>31</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -1559,7 +1641,7 @@
   <sheetData>
     <row r="1" ht="48" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B1" s="4" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
@@ -1570,7 +1652,7 @@
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -1583,51 +1665,51 @@
     <row r="3" ht="8" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="F5" s="10">
         <v>1240</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="H5" s="9" t="s">
         <v>1</v>
@@ -1635,25 +1717,25 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="F6" s="14">
         <v>150</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="H6" s="13" t="s">
         <v>1</v>
@@ -1661,25 +1743,25 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="F7" s="10">
         <v>890</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="H7" s="9" t="s">
         <v>1</v>
@@ -1687,25 +1769,25 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="F8" s="14">
         <v>120</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="H8" s="13" t="s">
         <v>1</v>
@@ -1713,25 +1795,25 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="F9" s="16">
         <v>45</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="H9" s="9" t="s">
         <v>1</v>
@@ -1739,25 +1821,25 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="F10" s="18">
         <v>1560</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="H10" s="13" t="s">
         <v>1</v>
@@ -1765,25 +1847,25 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="F11" s="16">
         <v>180</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="H11" s="9" t="s">
         <v>1</v>
@@ -1791,25 +1873,25 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="F12" s="14">
         <v>340</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="H12" s="13" t="s">
         <v>1</v>
@@ -1817,51 +1899,51 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="F13" s="16">
         <v>225</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="F14" s="14">
         <v>195</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="H14" s="13" t="s">
         <v>1</v>
@@ -1869,25 +1951,25 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C15" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="D15" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="D15" s="9" t="s">
-        <v>61</v>
-      </c>
       <c r="E15" s="9" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="F15" s="16">
         <v>210</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="H15" s="9" t="s">
         <v>1</v>
@@ -1895,25 +1977,25 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="F16" s="18">
         <v>980</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="H16" s="13" t="s">
         <v>1</v>
@@ -1921,25 +2003,25 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="F17" s="16">
         <v>150</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="H17" s="9" t="s">
         <v>1</v>
@@ -1947,25 +2029,25 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="F18" s="14">
         <v>185</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="H18" s="13" t="s">
         <v>1</v>
@@ -1973,25 +2055,25 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="F19" s="16">
         <v>210</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="H19" s="9" t="s">
         <v>1</v>
@@ -1999,25 +2081,25 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="F20" s="14">
         <v>195</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="H20" s="13" t="s">
         <v>1</v>
@@ -2025,25 +2107,25 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="F21" s="10">
         <v>2100</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="H21" s="9" t="s">
         <v>1</v>
@@ -2051,25 +2133,25 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="F22" s="14">
         <v>140</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="H22" s="13" t="s">
         <v>1</v>
@@ -2077,85 +2159,160 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="F23" s="16">
         <v>67</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="F24" s="14">
         <v>90</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="F25" s="16">
         <v>47</v>
       </c>
       <c r="G25" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="B26" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="D26" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="H25" s="9" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.25"/>
+      <c r="E26" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="F26" s="18">
+        <v>1000</v>
+      </c>
+      <c r="G26" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="H26" s="13" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="B27" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="F27" s="16">
+        <v>155</v>
+      </c>
+      <c r="G27" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="H27" s="9" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="F28" s="14">
+        <v>150</v>
+      </c>
+      <c r="G28" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="H28" s="13" t="s">
+        <v>1</v>
+      </c>
+    </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.25"/>
     <row r="30" spans="2:7" x14ac:dyDescent="0.25"/>
     <row r="31" spans="2:7" x14ac:dyDescent="0.25"/>
@@ -2671,7 +2828,7 @@
   <sheetData>
     <row r="1" ht="48" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B1" s="4" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
@@ -2682,7 +2839,7 @@
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -2695,51 +2852,51 @@
     <row r="3" ht="8" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" ht="28" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="E4" s="19" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="F4" s="19" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="G4" s="19" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="H4" s="19" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="I4" s="19" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="J4" s="19" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="K4" s="19" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="L4" s="19" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="M4" s="19" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="N4" s="19" t="s">
-        <v>100</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="20" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="B5" s="21">
         <f>SUMPRODUCT((MONTH('Revenue &amp; Expenses'!A5:A500)=1)*(YEAR('Revenue &amp; Expenses'!A5:A500)=2026)*('Revenue &amp; Expenses'!B5:B500="Revenue")*'Revenue &amp; Expenses'!F5:F500)</f>
@@ -2783,7 +2940,7 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="20" t="s">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="B6" s="21">
         <f>SUMPRODUCT((MONTH('Revenue &amp; Expenses'!A5:A500)=1)*(YEAR('Revenue &amp; Expenses'!A5:A500)=2026)*('Revenue &amp; Expenses'!B5:B500="Expense")*'Revenue &amp; Expenses'!F5:F500)</f>
@@ -2827,7 +2984,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="23" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="B7" s="24">
         <f>B5-B6</f>
@@ -2871,7 +3028,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="20" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="B8" s="25">
         <f>IF(B5=0,0,B7/B5)</f>
@@ -2915,7 +3072,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="20" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="B9" s="9">
         <f>SUMPRODUCT((MONTH('Revenue &amp; Expenses'!A5:A500)=1)*(YEAR('Revenue &amp; Expenses'!A5:A500)=2026)*('Revenue &amp; Expenses'!B5:B500&lt;&gt;""))</f>
@@ -2959,7 +3116,7 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="20" t="s">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="B10" s="21">
         <f>IF(SUMPRODUCT((MONTH('Revenue &amp; Expenses'!A5:A500)=1)*(YEAR('Revenue &amp; Expenses'!A5:A500)=2026)*('Revenue &amp; Expenses'!B5:B500="Revenue"))=0,0,B5/SUMPRODUCT((MONTH('Revenue &amp; Expenses'!A5:A500)=1)*(YEAR('Revenue &amp; Expenses'!A5:A500)=2026)*('Revenue &amp; Expenses'!B5:B500="Revenue")))</f>
@@ -3027,7 +3184,7 @@
   <sheetData>
     <row r="1" ht="48" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B1" s="4" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
@@ -3038,7 +3195,7 @@
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -3051,33 +3208,33 @@
     <row r="3" ht="8" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="27" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="B4" s="27" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="D4" s="27" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="E4" s="27" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="F4" s="27" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="G4" s="27" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="H4" s="27" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="20" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B5" s="28">
         <f>SUMPRODUCT(('Revenue &amp; Expenses'!D5:D500="Downtown Loft")*('Revenue &amp; Expenses'!B5:B500="Revenue")*'Revenue &amp; Expenses'!F5:F500)</f>
@@ -3100,7 +3257,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="30" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="B6" s="31">
         <f>SUMPRODUCT(('Revenue &amp; Expenses'!D5:D500="Lakeside Cabin")*('Revenue &amp; Expenses'!B5:B500="Revenue")*'Revenue &amp; Expenses'!F5:F500)</f>
@@ -3124,7 +3281,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="20" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="B7" s="28">
         <f>SUMPRODUCT(('Revenue &amp; Expenses'!D5:D500="Beach Bungalow")*('Revenue &amp; Expenses'!B5:B500="Revenue")*'Revenue &amp; Expenses'!F5:F500)</f>
@@ -3147,7 +3304,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="34" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="B8" s="35">
         <f>SUM(B5:B7)</f>
@@ -3193,7 +3350,7 @@
   <sheetData>
     <row r="1" ht="48" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B1" s="4" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
@@ -3204,7 +3361,7 @@
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -3217,12 +3374,12 @@
     <row r="3" ht="8" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="37" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5" s="9" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="C5" s="20">
         <v>2026</v>
@@ -3230,7 +3387,7 @@
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="9" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="C6" s="20">
         <v>280</v>
@@ -3238,7 +3395,7 @@
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B7" s="9" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="C7" s="20">
         <v>30</v>
@@ -3246,7 +3403,7 @@
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" s="9" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="C8" s="26">
         <f>C6/(C6+C7)</f>
@@ -3255,30 +3412,30 @@
     <row r="10" ht="8" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="11" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="38" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="B11" s="38" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="C11" s="38" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="D11" s="38" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="E11" s="38" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="39" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="D12" s="28">
         <f>SUMPRODUCT(('Revenue &amp; Expenses'!C5:C500="Airbnb Payout")*('Revenue &amp; Expenses'!B5:B500="Revenue")*'Revenue &amp; Expenses'!F5:F500)+SUMPRODUCT(('Revenue &amp; Expenses'!C5:C500="VRBO Payout")*('Revenue &amp; Expenses'!B5:B500="Revenue")*'Revenue &amp; Expenses'!F5:F500)+SUMPRODUCT(('Revenue &amp; Expenses'!C5:C500="Other Revenue")*('Revenue &amp; Expenses'!B5:B500="Revenue")*'Revenue &amp; Expenses'!F5:F500)</f>
@@ -3289,13 +3446,13 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="40" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="C13" s="41" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="D13" s="31">
         <f>SUMPRODUCT(('Revenue &amp; Expenses'!C5:C500="Advertising")*('Revenue &amp; Expenses'!B5:B500="Expense")*'Revenue &amp; Expenses'!F5:F500)</f>
@@ -3306,13 +3463,13 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="39" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D14" s="28">
         <f>SUMPRODUCT(('Revenue &amp; Expenses'!C5:C500="Cleaning")*('Revenue &amp; Expenses'!B5:B500="Expense")*'Revenue &amp; Expenses'!F5:F500)</f>
@@ -3323,13 +3480,13 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="40" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="C15" s="41" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="D15" s="31">
         <f>SUMPRODUCT(('Revenue &amp; Expenses'!C5:C500="Platform Fees")*('Revenue &amp; Expenses'!B5:B500="Expense")*'Revenue &amp; Expenses'!F5:F500)+SUMPRODUCT(('Revenue &amp; Expenses'!C5:C500="Management Fees")*('Revenue &amp; Expenses'!B5:B500="Expense")*'Revenue &amp; Expenses'!F5:F500)</f>
@@ -3340,13 +3497,13 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="39" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D16" s="28">
         <f>SUMPRODUCT(('Revenue &amp; Expenses'!C5:C500="Insurance")*('Revenue &amp; Expenses'!B5:B500="Expense")*'Revenue &amp; Expenses'!F5:F500)</f>
@@ -3357,13 +3514,13 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="40" t="s">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="C17" s="41" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="D17" s="31">
         <f>SUMPRODUCT(('Revenue &amp; Expenses'!C5:C500="Mortgage Interest")*('Revenue &amp; Expenses'!B5:B500="Expense")*'Revenue &amp; Expenses'!F5:F500)</f>
@@ -3374,13 +3531,13 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="39" t="s">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="D18" s="28">
         <f>SUMPRODUCT(('Revenue &amp; Expenses'!C5:C500="Maintenance &amp; Repairs")*('Revenue &amp; Expenses'!B5:B500="Expense")*'Revenue &amp; Expenses'!F5:F500)</f>
@@ -3391,13 +3548,13 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="40" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="C19" s="41" t="s">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="D19" s="31">
         <f>SUMPRODUCT(('Revenue &amp; Expenses'!C5:C500="Property Tax")*('Revenue &amp; Expenses'!B5:B500="Expense")*'Revenue &amp; Expenses'!F5:F500)</f>
@@ -3408,13 +3565,13 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="39" t="s">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="D20" s="28">
         <f>SUMPRODUCT(('Revenue &amp; Expenses'!C5:C500="Utilities")*('Revenue &amp; Expenses'!B5:B500="Expense")*'Revenue &amp; Expenses'!F5:F500)</f>
@@ -3425,13 +3582,13 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="40" t="s">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>146</v>
+        <v>160</v>
       </c>
       <c r="C21" s="41" t="s">
-        <v>146</v>
+        <v>160</v>
       </c>
       <c r="D21" s="31">
         <f>SUMPRODUCT(('Revenue &amp; Expenses'!C5:C500="Depreciation")*('Revenue &amp; Expenses'!B5:B500="Expense")*'Revenue &amp; Expenses'!F5:F500)</f>
@@ -3442,13 +3599,13 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="39" t="s">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>148</v>
+        <v>162</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="D22" s="28">
         <f>SUMPRODUCT(('Revenue &amp; Expenses'!C5:C500="Supplies")*('Revenue &amp; Expenses'!B5:B500="Expense")*'Revenue &amp; Expenses'!F5:F500)+SUMPRODUCT(('Revenue &amp; Expenses'!C5:C500="Other Expense")*('Revenue &amp; Expenses'!B5:B500="Expense")*'Revenue &amp; Expenses'!F5:F500)</f>
@@ -3460,7 +3617,7 @@
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="42"/>
       <c r="B23" s="42" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="C23" s="42"/>
       <c r="D23" s="43">
@@ -3473,7 +3630,7 @@
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="44"/>
       <c r="B24" s="44" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="C24" s="44"/>
       <c r="D24" s="44"/>
@@ -3509,7 +3666,7 @@
   <sheetData>
     <row r="1" ht="48" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B1" s="4" t="s">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
@@ -3520,7 +3677,7 @@
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -3533,42 +3690,42 @@
     <row r="3" ht="8" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="46" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="B4" s="46" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="C4" s="46" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="D4" s="46" t="s">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="E4" s="46" t="s">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="F4" s="46" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="G4" s="46" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="H4" s="46" t="s">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="I4" s="46" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="D5" s="9">
         <v>2.5</v>
@@ -3577,10 +3734,10 @@
         <v>150</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="H5" s="9">
         <v>4</v>
@@ -3591,13 +3748,13 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="D6" s="13">
         <v>2</v>
@@ -3606,27 +3763,27 @@
         <v>120</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="H6" s="13">
         <v>5</v>
       </c>
       <c r="I6" s="13" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="D7" s="9">
         <v>3</v>
@@ -3635,27 +3792,27 @@
         <v>180</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="H7" s="9">
         <v>4</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="D8" s="13">
         <v>2.5</v>
@@ -3664,10 +3821,10 @@
         <v>150</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="H8" s="13">
         <v>4</v>
@@ -3678,13 +3835,13 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="D9" s="9">
         <v>2.5</v>
@@ -3693,28 +3850,28 @@
         <v>140</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="H9" s="9">
         <v>5</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
     </row>
     <row r="10" spans="7:8" x14ac:dyDescent="0.25"/>
     <row r="11" spans="7:8" x14ac:dyDescent="0.25"/>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="48" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="B13" s="20">
         <f>COUNTA(A5:A9)</f>
@@ -3722,7 +3879,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="B14" s="22">
         <f>SUM(E5:E9)</f>
@@ -3730,7 +3887,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="B15" s="22">
         <f>IF(B13=0,0,B14/B13)</f>
@@ -3738,7 +3895,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="B16" s="20">
         <f>IF(B13=0,0,AVERAGE(D5:D9))</f>
@@ -3746,7 +3903,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="B17" s="22">
         <f>IF(B16=0,0,B15/B16)</f>
